--- a/Día 13-Crear un sistema de Atención de pacientes médicos/Salarios_parte2.xlsx
+++ b/Día 13-Crear un sistema de Atención de pacientes médicos/Salarios_parte2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUSTAVO\Documents\Cursos Udemy\ExcelTotal\Día 13-Crear un sistema de Atención de pacientes médicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0609A185-8B0D-4B83-AF43-005B731DD421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C83E1EE-3A5C-4670-AB65-3BBC404E39C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="477">
   <si>
     <t>Nombre</t>
   </si>
@@ -1430,9 +1430,6 @@
     <t>Mail</t>
   </si>
   <si>
-    <t>mail_falso@excel.com</t>
-  </si>
-  <si>
     <t>Evelyn Diaz</t>
   </si>
   <si>
@@ -1479,6 +1476,9 @@
   </si>
   <si>
     <t>Email</t>
+  </si>
+  <si>
+    <t>gmail.com</t>
   </si>
 </sst>
 </file>
@@ -2220,7 +2220,7 @@
     <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" customWidth="1"/>
     <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.6640625" customWidth="1"/>
     <col min="7" max="7" width="11.5546875" customWidth="1"/>
     <col min="9" max="9" width="11.5546875" customWidth="1"/>
@@ -2262,7 +2262,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="17">
-        <v>1967</v>
+        <v>1078</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="18" t="s">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="E5" s="17" t="str">
         <f>VLOOKUP($B$5,'Base de datos'!$A$1:$J$115,7,FALSE)</f>
-        <v>Administrativo</v>
+        <v>Docente</v>
       </c>
       <c r="F5" s="19"/>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B7" s="17" t="str">
         <f>VLOOKUP($B$5,'Base de datos'!$A$1:$J$115,2,FALSE)</f>
-        <v>Santiago</v>
+        <v>Rafael</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="18" t="s">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="E7" s="20">
         <f>VLOOKUP($B$5,'Base de datos'!$A$1:$J$115,8,FALSE)</f>
-        <v>2600000</v>
+        <v>3200000</v>
       </c>
       <c r="F7" s="19"/>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B9" s="17" t="str">
         <f>VLOOKUP($B$5,'Base de datos'!$A$1:$J$115,3,FALSE)</f>
-        <v>Betancurt</v>
+        <v>Cortes</v>
       </c>
       <c r="C9" s="24"/>
       <c r="D9" s="18" t="s">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="E9" s="21">
         <f>VLOOKUP($B$5,'Base de datos'!$A$1:$J$115,9,FALSE)</f>
-        <v>32771</v>
+        <v>32032</v>
       </c>
       <c r="F9" s="19"/>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="E11" s="21">
         <f>VLOOKUP($B$5,'Base de datos'!$A$1:$J$115,10,FALSE)</f>
-        <v>22172</v>
+        <v>22565</v>
       </c>
       <c r="F11" s="19"/>
     </row>
@@ -2366,15 +2366,15 @@
       </c>
       <c r="B13" s="17" t="str">
         <f>VLOOKUP($B$5,'Base de datos'!$A$1:$J$115,6,FALSE)</f>
-        <v>Diseño</v>
+        <v>Ingeniería</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E13" s="41">
         <f>VLOOKUP(CONCATENATE($B$7," ",$B$9),Contactos!A1:C115,2,FALSE)</f>
-        <v>5559904</v>
+        <v>5559810</v>
       </c>
       <c r="F13" s="19"/>
     </row>
@@ -2392,15 +2392,15 @@
       </c>
       <c r="B15" s="17" t="str">
         <f>VLOOKUP($B$5,'Salarios-Domicilios'!$A$1:$D$115,2,FALSE)</f>
-        <v>Calle Inventada 105</v>
+        <v>Calle Inventada 11</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="18" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E15" s="42" t="str">
         <f>VLOOKUP(CONCATENATE($B$7," ",$B$9),Contactos!A1:C115,3,FALSE)</f>
-        <v>mail_falso@excel.com</v>
+        <v>RafaelCortes@gmail.com</v>
       </c>
       <c r="F15" s="19"/>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B17" s="17" t="str">
         <f>VLOOKUP($B$5,'Salarios-Domicilios'!$A$1:$D$115,3,FALSE)</f>
-        <v>Bucaramanga</v>
+        <v>Palmira</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="24"/>
@@ -6503,10 +6503,10 @@
         <v>358</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -6517,10 +6517,10 @@
         <v>359</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -6531,10 +6531,10 @@
         <v>360</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -6545,10 +6545,10 @@
         <v>361</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -6559,10 +6559,10 @@
         <v>362</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -6573,10 +6573,10 @@
         <v>363</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -6587,10 +6587,10 @@
         <v>364</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -6601,10 +6601,10 @@
         <v>365</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -6615,10 +6615,10 @@
         <v>366</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -6629,10 +6629,10 @@
         <v>367</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -6643,10 +6643,10 @@
         <v>368</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -6657,10 +6657,10 @@
         <v>369</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D29" s="30" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -6797,10 +6797,10 @@
         <v>379</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D39" s="30" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -7888,15 +7888,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{391C3B96-DD32-4E92-B170-577058683DBF}">
-  <dimension ref="A1:C115"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
         <v>457</v>
       </c>
@@ -7907,169 +7909,187 @@
         <v>459</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
         <v>66</v>
       </c>
       <c r="B2" s="31">
         <v>5559800</v>
       </c>
-      <c r="C2" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" t="str">
+        <f>_xlfn.CONCAT(SUBSTITUTE(A2," ",""),"@",$E$2)</f>
+        <v>LuisaSierra@gmail.com</v>
+      </c>
+      <c r="E2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
         <v>88</v>
       </c>
       <c r="B3" s="31">
         <v>5559801</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" t="str">
+        <f t="shared" ref="C3:C66" si="0">_xlfn.CONCAT(SUBSTITUTE(A3," ",""),"@",$E$2)</f>
+        <v>JulianDuque@gmail.com</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
         <v>104</v>
       </c>
       <c r="B4" s="31">
         <v>5559802</v>
       </c>
-      <c r="C4" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>AmaliaGutierrez@gmail.com</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
         <v>125</v>
       </c>
       <c r="B5" s="31">
         <v>5559803</v>
       </c>
-      <c r="C5" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>MiguelSuarez@gmail.com</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
         <v>124</v>
       </c>
       <c r="B6" s="31">
         <v>5559804</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>AdrianaHoyos@gmail.com</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
         <v>38</v>
       </c>
       <c r="B7" s="31">
         <v>5559805</v>
       </c>
-      <c r="C7" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>JavierSantana@gmail.com</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
         <v>83</v>
       </c>
       <c r="B8" s="31">
         <v>5559806</v>
       </c>
-      <c r="C8" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>DaliaLemos@gmail.com</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
         <v>87</v>
       </c>
       <c r="B9" s="31">
         <v>5559807</v>
       </c>
-      <c r="C9" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v>AmaliaVergara@gmail.com</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
         <v>126</v>
       </c>
       <c r="B10" s="31">
         <v>5559808</v>
       </c>
-      <c r="C10" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v>NataliaAristizabal@gmail.com</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="31">
         <v>5559809</v>
       </c>
-      <c r="C11" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v>JorgeIdarraga@gmail.com</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="31">
         <v>5559810</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v>RafaelCortes@gmail.com</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="32" t="s">
         <v>57</v>
       </c>
       <c r="B13" s="31">
         <v>5559811</v>
       </c>
-      <c r="C13" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v>ElenaPerez@gmail.com</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="32" t="s">
         <v>132</v>
       </c>
       <c r="B14" s="31">
         <v>5559812</v>
       </c>
-      <c r="C14" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v>JacoboBustos@gmail.com</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="32" t="s">
         <v>56</v>
       </c>
       <c r="B15" s="31">
         <v>5559813</v>
       </c>
-      <c r="C15" s="32" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v>AlbertoPeláez@gmail.com</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="32" t="s">
         <v>63</v>
       </c>
       <c r="B16" s="31">
         <v>5559814</v>
       </c>
-      <c r="C16" s="32" t="s">
-        <v>460</v>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v>TomasRamirez@gmail.com</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -8079,8 +8099,9 @@
       <c r="B17" s="31">
         <v>5559815</v>
       </c>
-      <c r="C17" s="32" t="s">
-        <v>460</v>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>AngelinaPulgarin@gmail.com</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -8090,8 +8111,9 @@
       <c r="B18" s="31">
         <v>5559816</v>
       </c>
-      <c r="C18" s="32" t="s">
-        <v>460</v>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>JuanArango@gmail.com</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -8101,8 +8123,9 @@
       <c r="B19" s="31">
         <v>5559817</v>
       </c>
-      <c r="C19" s="32" t="s">
-        <v>460</v>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>MariaLema@gmail.com</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -8112,8 +8135,9 @@
       <c r="B20" s="31">
         <v>5559818</v>
       </c>
-      <c r="C20" s="32" t="s">
-        <v>460</v>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v>MonicaCastro@gmail.com</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -8123,8 +8147,9 @@
       <c r="B21" s="31">
         <v>5559819</v>
       </c>
-      <c r="C21" s="32" t="s">
-        <v>460</v>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v>AntonioMerizalde@gmail.com</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -8134,8 +8159,9 @@
       <c r="B22" s="31">
         <v>5559820</v>
       </c>
-      <c r="C22" s="32" t="s">
-        <v>460</v>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v>FranciscoArias@gmail.com</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -8145,8 +8171,9 @@
       <c r="B23" s="31">
         <v>5559821</v>
       </c>
-      <c r="C23" s="32" t="s">
-        <v>460</v>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v>OscarCifuentes@gmail.com</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -8156,8 +8183,9 @@
       <c r="B24" s="31">
         <v>5559822</v>
       </c>
-      <c r="C24" s="32" t="s">
-        <v>460</v>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v>CarmenUribe@gmail.com</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -8167,8 +8195,9 @@
       <c r="B25" s="31">
         <v>5559823</v>
       </c>
-      <c r="C25" s="32" t="s">
-        <v>460</v>
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v>IsabelSalamanca@gmail.com</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -8178,8 +8207,9 @@
       <c r="B26" s="31">
         <v>5559824</v>
       </c>
-      <c r="C26" s="32" t="s">
-        <v>460</v>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v>KarinaJimenez@gmail.com</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -8189,8 +8219,9 @@
       <c r="B27" s="31">
         <v>5559825</v>
       </c>
-      <c r="C27" s="32" t="s">
-        <v>460</v>
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v>BrendaAguirre@gmail.com</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -8200,8 +8231,9 @@
       <c r="B28" s="31">
         <v>5559826</v>
       </c>
-      <c r="C28" s="32" t="s">
-        <v>460</v>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v>CatalinaOsorio@gmail.com</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -8211,8 +8243,9 @@
       <c r="B29" s="31">
         <v>5559827</v>
       </c>
-      <c r="C29" s="32" t="s">
-        <v>460</v>
+      <c r="C29" t="str">
+        <f t="shared" si="0"/>
+        <v>CarlosGomez@gmail.com</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -8222,8 +8255,9 @@
       <c r="B30" s="31">
         <v>5559828</v>
       </c>
-      <c r="C30" s="32" t="s">
-        <v>460</v>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v>ManuelaCasadiegos@gmail.com</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -8233,8 +8267,9 @@
       <c r="B31" s="31">
         <v>5559829</v>
       </c>
-      <c r="C31" s="32" t="s">
-        <v>460</v>
+      <c r="C31" t="str">
+        <f t="shared" si="0"/>
+        <v>MaritzaMuñoz@gmail.com</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -8244,8 +8279,9 @@
       <c r="B32" s="31">
         <v>5559830</v>
       </c>
-      <c r="C32" s="32" t="s">
-        <v>460</v>
+      <c r="C32" t="str">
+        <f t="shared" si="0"/>
+        <v>ElisaMota@gmail.com</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -8255,8 +8291,9 @@
       <c r="B33" s="31">
         <v>5559831</v>
       </c>
-      <c r="C33" s="32" t="s">
-        <v>460</v>
+      <c r="C33" t="str">
+        <f t="shared" si="0"/>
+        <v>DinaraLopez@gmail.com</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -8266,8 +8303,9 @@
       <c r="B34" s="31">
         <v>5559832</v>
       </c>
-      <c r="C34" s="32" t="s">
-        <v>460</v>
+      <c r="C34" t="str">
+        <f t="shared" si="0"/>
+        <v>AlejandraFlorez@gmail.com</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -8277,8 +8315,9 @@
       <c r="B35" s="31">
         <v>5559833</v>
       </c>
-      <c r="C35" s="32" t="s">
-        <v>460</v>
+      <c r="C35" t="str">
+        <f t="shared" si="0"/>
+        <v>JesusBermudez@gmail.com</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -8288,8 +8327,9 @@
       <c r="B36" s="31">
         <v>5559834</v>
       </c>
-      <c r="C36" s="32" t="s">
-        <v>460</v>
+      <c r="C36" t="str">
+        <f t="shared" si="0"/>
+        <v>JuliethOsorio@gmail.com</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -8299,8 +8339,9 @@
       <c r="B37" s="31">
         <v>5559835</v>
       </c>
-      <c r="C37" s="32" t="s">
-        <v>460</v>
+      <c r="C37" t="str">
+        <f t="shared" si="0"/>
+        <v>ElianaRamirez@gmail.com</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -8310,8 +8351,9 @@
       <c r="B38" s="31">
         <v>5559836</v>
       </c>
-      <c r="C38" s="32" t="s">
-        <v>460</v>
+      <c r="C38" t="str">
+        <f t="shared" si="0"/>
+        <v>JulianaCastrillón@gmail.com</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -8321,8 +8363,9 @@
       <c r="B39" s="31">
         <v>5559837</v>
       </c>
-      <c r="C39" s="32" t="s">
-        <v>460</v>
+      <c r="C39" t="str">
+        <f t="shared" si="0"/>
+        <v>CarolinaCano@gmail.com</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -8332,8 +8375,9 @@
       <c r="B40" s="31">
         <v>5559838</v>
       </c>
-      <c r="C40" s="32" t="s">
-        <v>460</v>
+      <c r="C40" t="str">
+        <f t="shared" si="0"/>
+        <v>AliciaPerez@gmail.com</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -8343,8 +8387,9 @@
       <c r="B41" s="31">
         <v>5559839</v>
       </c>
-      <c r="C41" s="32" t="s">
-        <v>460</v>
+      <c r="C41" t="str">
+        <f t="shared" si="0"/>
+        <v>ManuelToro@gmail.com</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -8354,8 +8399,9 @@
       <c r="B42" s="31">
         <v>5559840</v>
       </c>
-      <c r="C42" s="32" t="s">
-        <v>460</v>
+      <c r="C42" t="str">
+        <f t="shared" si="0"/>
+        <v>GabrielRodas@gmail.com</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -8365,8 +8411,9 @@
       <c r="B43" s="31">
         <v>5559841</v>
       </c>
-      <c r="C43" s="32" t="s">
-        <v>460</v>
+      <c r="C43" t="str">
+        <f t="shared" si="0"/>
+        <v>SusanaRuiz@gmail.com</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -8376,8 +8423,9 @@
       <c r="B44" s="31">
         <v>5559842</v>
       </c>
-      <c r="C44" s="32" t="s">
-        <v>460</v>
+      <c r="C44" t="str">
+        <f t="shared" si="0"/>
+        <v>SaraVallejo@gmail.com</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -8387,8 +8435,9 @@
       <c r="B45" s="31">
         <v>5559843</v>
       </c>
-      <c r="C45" s="32" t="s">
-        <v>460</v>
+      <c r="C45" t="str">
+        <f t="shared" si="0"/>
+        <v>GustavoMendez@gmail.com</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -8398,8 +8447,9 @@
       <c r="B46" s="31">
         <v>5559844</v>
       </c>
-      <c r="C46" s="32" t="s">
-        <v>460</v>
+      <c r="C46" t="str">
+        <f t="shared" si="0"/>
+        <v>RaquelMedina@gmail.com</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -8409,8 +8459,9 @@
       <c r="B47" s="31">
         <v>5559845</v>
       </c>
-      <c r="C47" s="32" t="s">
-        <v>460</v>
+      <c r="C47" t="str">
+        <f t="shared" si="0"/>
+        <v>TammyMendez@gmail.com</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -8420,30 +8471,33 @@
       <c r="B48" s="31">
         <v>5559846</v>
       </c>
-      <c r="C48" s="32" t="s">
-        <v>460</v>
+      <c r="C48" t="str">
+        <f t="shared" si="0"/>
+        <v>SandraCano@gmail.com</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="32" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B49" s="31">
         <v>5559847</v>
       </c>
-      <c r="C49" s="32" t="s">
-        <v>460</v>
+      <c r="C49" t="str">
+        <f t="shared" si="0"/>
+        <v>EvelynDiaz@gmail.com</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="32" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B50" s="31">
         <v>5559848</v>
       </c>
-      <c r="C50" s="32" t="s">
-        <v>460</v>
+      <c r="C50" t="str">
+        <f t="shared" si="0"/>
+        <v>PabloRojas@gmail.com</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -8453,8 +8507,9 @@
       <c r="B51" s="31">
         <v>5559849</v>
       </c>
-      <c r="C51" s="32" t="s">
-        <v>460</v>
+      <c r="C51" t="str">
+        <f t="shared" si="0"/>
+        <v>DavidJaramillo@gmail.com</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -8464,8 +8519,9 @@
       <c r="B52" s="31">
         <v>5559850</v>
       </c>
-      <c r="C52" s="32" t="s">
-        <v>460</v>
+      <c r="C52" t="str">
+        <f t="shared" si="0"/>
+        <v>GloriaTamayo@gmail.com</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -8475,8 +8531,9 @@
       <c r="B53" s="31">
         <v>5559851</v>
       </c>
-      <c r="C53" s="32" t="s">
-        <v>460</v>
+      <c r="C53" t="str">
+        <f t="shared" si="0"/>
+        <v>PamelaSerna@gmail.com</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -8486,8 +8543,9 @@
       <c r="B54" s="31">
         <v>5559852</v>
       </c>
-      <c r="C54" s="32" t="s">
-        <v>460</v>
+      <c r="C54" t="str">
+        <f t="shared" si="0"/>
+        <v>JessicaMarquez@gmail.com</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -8497,8 +8555,9 @@
       <c r="B55" s="31">
         <v>5559853</v>
       </c>
-      <c r="C55" s="32" t="s">
-        <v>460</v>
+      <c r="C55" t="str">
+        <f t="shared" si="0"/>
+        <v>GuillermoFernandez@gmail.com</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -8508,8 +8567,9 @@
       <c r="B56" s="31">
         <v>5559854</v>
       </c>
-      <c r="C56" s="32" t="s">
-        <v>460</v>
+      <c r="C56" t="str">
+        <f t="shared" si="0"/>
+        <v>KarenRestrepo@gmail.com</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -8519,8 +8579,9 @@
       <c r="B57" s="31">
         <v>5559855</v>
       </c>
-      <c r="C57" s="32" t="s">
-        <v>460</v>
+      <c r="C57" t="str">
+        <f t="shared" si="0"/>
+        <v>LeonardoVasquez@gmail.com</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -8530,8 +8591,9 @@
       <c r="B58" s="31">
         <v>5559856</v>
       </c>
-      <c r="C58" s="32" t="s">
-        <v>460</v>
+      <c r="C58" t="str">
+        <f t="shared" si="0"/>
+        <v>MarianaGomez@gmail.com</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -8541,8 +8603,9 @@
       <c r="B59" s="31">
         <v>5559857</v>
       </c>
-      <c r="C59" s="32" t="s">
-        <v>460</v>
+      <c r="C59" t="str">
+        <f t="shared" si="0"/>
+        <v>DanielOspina@gmail.com</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -8552,8 +8615,9 @@
       <c r="B60" s="31">
         <v>5559858</v>
       </c>
-      <c r="C60" s="32" t="s">
-        <v>460</v>
+      <c r="C60" t="str">
+        <f t="shared" si="0"/>
+        <v>AngelaAlzate@gmail.com</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -8563,8 +8627,9 @@
       <c r="B61" s="31">
         <v>5559859</v>
       </c>
-      <c r="C61" s="32" t="s">
-        <v>460</v>
+      <c r="C61" t="str">
+        <f t="shared" si="0"/>
+        <v>AndrésPeláez@gmail.com</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -8574,8 +8639,9 @@
       <c r="B62" s="31">
         <v>5559860</v>
       </c>
-      <c r="C62" s="32" t="s">
-        <v>460</v>
+      <c r="C62" t="str">
+        <f t="shared" si="0"/>
+        <v>SimónGracía@gmail.com</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -8585,8 +8651,9 @@
       <c r="B63" s="31">
         <v>5559861</v>
       </c>
-      <c r="C63" s="32" t="s">
-        <v>460</v>
+      <c r="C63" t="str">
+        <f t="shared" si="0"/>
+        <v>SofiaMarulanda@gmail.com</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -8596,8 +8663,9 @@
       <c r="B64" s="31">
         <v>5559862</v>
       </c>
-      <c r="C64" s="32" t="s">
-        <v>460</v>
+      <c r="C64" t="str">
+        <f t="shared" si="0"/>
+        <v>LinaVillamizar@gmail.com</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -8607,8 +8675,9 @@
       <c r="B65" s="31">
         <v>5559863</v>
       </c>
-      <c r="C65" s="32" t="s">
-        <v>460</v>
+      <c r="C65" t="str">
+        <f t="shared" si="0"/>
+        <v>MarcelaSantis@gmail.com</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -8618,8 +8687,9 @@
       <c r="B66" s="31">
         <v>5559864</v>
       </c>
-      <c r="C66" s="32" t="s">
-        <v>460</v>
+      <c r="C66" t="str">
+        <f t="shared" si="0"/>
+        <v>SamuelRico@gmail.com</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -8629,8 +8699,9 @@
       <c r="B67" s="31">
         <v>5559865</v>
       </c>
-      <c r="C67" s="32" t="s">
-        <v>460</v>
+      <c r="C67" t="str">
+        <f t="shared" ref="C67:C115" si="1">_xlfn.CONCAT(SUBSTITUTE(A67," ",""),"@",$E$2)</f>
+        <v>TatianaArango@gmail.com</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -8640,8 +8711,9 @@
       <c r="B68" s="31">
         <v>5559866</v>
       </c>
-      <c r="C68" s="32" t="s">
-        <v>460</v>
+      <c r="C68" t="str">
+        <f t="shared" si="1"/>
+        <v>JoseCarmona@gmail.com</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -8651,8 +8723,9 @@
       <c r="B69" s="31">
         <v>5559867</v>
       </c>
-      <c r="C69" s="32" t="s">
-        <v>460</v>
+      <c r="C69" t="str">
+        <f t="shared" si="1"/>
+        <v>DanielaFranco@gmail.com</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -8662,8 +8735,9 @@
       <c r="B70" s="31">
         <v>5559868</v>
       </c>
-      <c r="C70" s="32" t="s">
-        <v>460</v>
+      <c r="C70" t="str">
+        <f t="shared" si="1"/>
+        <v>StepaniaZapata@gmail.com</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -8673,8 +8747,9 @@
       <c r="B71" s="31">
         <v>5559869</v>
       </c>
-      <c r="C71" s="32" t="s">
-        <v>460</v>
+      <c r="C71" t="str">
+        <f t="shared" si="1"/>
+        <v>EstefaniaVillegas@gmail.com</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -8684,19 +8759,21 @@
       <c r="B72" s="31">
         <v>5559870</v>
       </c>
-      <c r="C72" s="32" t="s">
-        <v>460</v>
+      <c r="C72" t="str">
+        <f t="shared" si="1"/>
+        <v>DavidLemus@gmail.com</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="32" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B73" s="31">
         <v>5559871</v>
       </c>
-      <c r="C73" s="32" t="s">
-        <v>460</v>
+      <c r="C73" t="str">
+        <f t="shared" si="1"/>
+        <v>JorgeZea@gmail.com</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -8706,8 +8783,9 @@
       <c r="B74" s="31">
         <v>5559872</v>
       </c>
-      <c r="C74" s="32" t="s">
-        <v>460</v>
+      <c r="C74" t="str">
+        <f t="shared" si="1"/>
+        <v>LuisMelano@gmail.com</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -8717,19 +8795,21 @@
       <c r="B75" s="31">
         <v>5559873</v>
       </c>
-      <c r="C75" s="32" t="s">
-        <v>460</v>
+      <c r="C75" t="str">
+        <f t="shared" si="1"/>
+        <v>SebastianCarmona@gmail.com</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="32" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B76" s="31">
         <v>5559874</v>
       </c>
-      <c r="C76" s="32" t="s">
-        <v>460</v>
+      <c r="C76" t="str">
+        <f t="shared" si="1"/>
+        <v>JuanHernandez@gmail.com</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -8739,8 +8819,9 @@
       <c r="B77" s="31">
         <v>5559875</v>
       </c>
-      <c r="C77" s="32" t="s">
-        <v>460</v>
+      <c r="C77" t="str">
+        <f t="shared" si="1"/>
+        <v>CamiloBerrio@gmail.com</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -8750,8 +8831,9 @@
       <c r="B78" s="31">
         <v>5559876</v>
       </c>
-      <c r="C78" s="32" t="s">
-        <v>460</v>
+      <c r="C78" t="str">
+        <f t="shared" si="1"/>
+        <v>CathyHiguita@gmail.com</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -8761,8 +8843,9 @@
       <c r="B79" s="31">
         <v>5559877</v>
       </c>
-      <c r="C79" s="32" t="s">
-        <v>460</v>
+      <c r="C79" t="str">
+        <f t="shared" si="1"/>
+        <v>EstebanGiraldo@gmail.com</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -8772,8 +8855,9 @@
       <c r="B80" s="31">
         <v>5559878</v>
       </c>
-      <c r="C80" s="32" t="s">
-        <v>460</v>
+      <c r="C80" t="str">
+        <f t="shared" si="1"/>
+        <v>AlexandraGuerrero@gmail.com</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -8783,8 +8867,9 @@
       <c r="B81" s="31">
         <v>5559879</v>
       </c>
-      <c r="C81" s="32" t="s">
-        <v>460</v>
+      <c r="C81" t="str">
+        <f t="shared" si="1"/>
+        <v>CristinaCock@gmail.com</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -8794,8 +8879,9 @@
       <c r="B82" s="31">
         <v>5559880</v>
       </c>
-      <c r="C82" s="32" t="s">
-        <v>460</v>
+      <c r="C82" t="str">
+        <f t="shared" si="1"/>
+        <v>SergioPosada@gmail.com</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -8805,8 +8891,9 @@
       <c r="B83" s="31">
         <v>5559881</v>
       </c>
-      <c r="C83" s="32" t="s">
-        <v>460</v>
+      <c r="C83" t="str">
+        <f t="shared" si="1"/>
+        <v>IsabellaMarquez@gmail.com</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -8816,8 +8903,9 @@
       <c r="B84" s="31">
         <v>5559882</v>
       </c>
-      <c r="C84" s="32" t="s">
-        <v>460</v>
+      <c r="C84" t="str">
+        <f t="shared" si="1"/>
+        <v>MelisaUribe@gmail.com</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -8827,19 +8915,21 @@
       <c r="B85" s="31">
         <v>5559883</v>
       </c>
-      <c r="C85" s="32" t="s">
-        <v>460</v>
+      <c r="C85" t="str">
+        <f t="shared" si="1"/>
+        <v>MauricioArango@gmail.com</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="32" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B86" s="31">
         <v>5559884</v>
       </c>
-      <c r="C86" s="32" t="s">
-        <v>460</v>
+      <c r="C86" t="str">
+        <f t="shared" si="1"/>
+        <v>MonicaArango@gmail.com</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -8849,30 +8939,33 @@
       <c r="B87" s="31">
         <v>5559885</v>
       </c>
-      <c r="C87" s="32" t="s">
-        <v>460</v>
+      <c r="C87" t="str">
+        <f t="shared" si="1"/>
+        <v>GonzaloBetancur@gmail.com</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="32" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B88" s="31">
         <v>5559886</v>
       </c>
-      <c r="C88" s="32" t="s">
-        <v>460</v>
+      <c r="C88" t="str">
+        <f t="shared" si="1"/>
+        <v>AnaRodríguez@gmail.com</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="32" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B89" s="31">
         <v>5559887</v>
       </c>
-      <c r="C89" s="32" t="s">
-        <v>460</v>
+      <c r="C89" t="str">
+        <f t="shared" si="1"/>
+        <v>AndreaCarmona@gmail.com</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -8882,8 +8975,9 @@
       <c r="B90" s="31">
         <v>5559888</v>
       </c>
-      <c r="C90" s="32" t="s">
-        <v>460</v>
+      <c r="C90" t="str">
+        <f t="shared" si="1"/>
+        <v>DianaCaro@gmail.com</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -8893,8 +8987,9 @@
       <c r="B91" s="31">
         <v>5559889</v>
       </c>
-      <c r="C91" s="32" t="s">
-        <v>460</v>
+      <c r="C91" t="str">
+        <f t="shared" si="1"/>
+        <v>AlejandroSimanca@gmail.com</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -8904,8 +8999,9 @@
       <c r="B92" s="31">
         <v>5559890</v>
       </c>
-      <c r="C92" s="32" t="s">
-        <v>460</v>
+      <c r="C92" t="str">
+        <f t="shared" si="1"/>
+        <v>RobertaToledo@gmail.com</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -8915,8 +9011,9 @@
       <c r="B93" s="31">
         <v>5559891</v>
       </c>
-      <c r="C93" s="32" t="s">
-        <v>460</v>
+      <c r="C93" t="str">
+        <f t="shared" si="1"/>
+        <v>MelinaAcevedo@gmail.com</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -8926,8 +9023,9 @@
       <c r="B94" s="31">
         <v>5559892</v>
       </c>
-      <c r="C94" s="32" t="s">
-        <v>460</v>
+      <c r="C94" t="str">
+        <f t="shared" si="1"/>
+        <v>PatriciaDiez@gmail.com</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -8937,8 +9035,9 @@
       <c r="B95" s="31">
         <v>5559893</v>
       </c>
-      <c r="C95" s="32" t="s">
-        <v>460</v>
+      <c r="C95" t="str">
+        <f t="shared" si="1"/>
+        <v>BarbaraHenao@gmail.com</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -8948,8 +9047,9 @@
       <c r="B96" s="31">
         <v>5559894</v>
       </c>
-      <c r="C96" s="32" t="s">
-        <v>460</v>
+      <c r="C96" t="str">
+        <f t="shared" si="1"/>
+        <v>LisaGuerra@gmail.com</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -8959,8 +9059,9 @@
       <c r="B97" s="31">
         <v>5559895</v>
       </c>
-      <c r="C97" s="32" t="s">
-        <v>460</v>
+      <c r="C97" t="str">
+        <f t="shared" si="1"/>
+        <v>FelipeArango@gmail.com</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -8970,8 +9071,9 @@
       <c r="B98" s="31">
         <v>5559896</v>
       </c>
-      <c r="C98" s="32" t="s">
-        <v>460</v>
+      <c r="C98" t="str">
+        <f t="shared" si="1"/>
+        <v>ElenaGarces@gmail.com</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -8981,8 +9083,9 @@
       <c r="B99" s="31">
         <v>5559897</v>
       </c>
-      <c r="C99" s="32" t="s">
-        <v>460</v>
+      <c r="C99" t="str">
+        <f t="shared" si="1"/>
+        <v>MiguelSanchez@gmail.com</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -8992,8 +9095,9 @@
       <c r="B100" s="31">
         <v>5559898</v>
       </c>
-      <c r="C100" s="32" t="s">
-        <v>460</v>
+      <c r="C100" t="str">
+        <f t="shared" si="1"/>
+        <v>PaulaPalacio@gmail.com</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -9003,8 +9107,9 @@
       <c r="B101" s="31">
         <v>5559899</v>
       </c>
-      <c r="C101" s="32" t="s">
-        <v>460</v>
+      <c r="C101" t="str">
+        <f t="shared" si="1"/>
+        <v>LuisaGranda@gmail.com</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -9014,8 +9119,9 @@
       <c r="B102" s="31">
         <v>5559900</v>
       </c>
-      <c r="C102" s="32" t="s">
-        <v>460</v>
+      <c r="C102" t="str">
+        <f t="shared" si="1"/>
+        <v>FelipeGirando@gmail.com</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -9025,8 +9131,9 @@
       <c r="B103" s="31">
         <v>5559901</v>
       </c>
-      <c r="C103" s="32" t="s">
-        <v>460</v>
+      <c r="C103" t="str">
+        <f t="shared" si="1"/>
+        <v>SantiagoJaramillo@gmail.com</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -9036,19 +9143,21 @@
       <c r="B104" s="31">
         <v>5559902</v>
       </c>
-      <c r="C104" s="32" t="s">
-        <v>460</v>
+      <c r="C104" t="str">
+        <f t="shared" si="1"/>
+        <v>HildaRodriguez@gmail.com</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="32" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B105" s="31">
         <v>5559903</v>
       </c>
-      <c r="C105" s="32" t="s">
-        <v>460</v>
+      <c r="C105" t="str">
+        <f t="shared" si="1"/>
+        <v>CamilaDominguez@gmail.com</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -9058,8 +9167,9 @@
       <c r="B106" s="31">
         <v>5559904</v>
       </c>
-      <c r="C106" s="32" t="s">
-        <v>460</v>
+      <c r="C106" t="str">
+        <f t="shared" si="1"/>
+        <v>SantiagoBetancurt@gmail.com</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -9069,8 +9179,9 @@
       <c r="B107" s="31">
         <v>5559905</v>
       </c>
-      <c r="C107" s="32" t="s">
-        <v>460</v>
+      <c r="C107" t="str">
+        <f t="shared" si="1"/>
+        <v>VictoriaHincapie@gmail.com</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -9080,19 +9191,21 @@
       <c r="B108" s="31">
         <v>5559906</v>
       </c>
-      <c r="C108" s="32" t="s">
-        <v>460</v>
+      <c r="C108" t="str">
+        <f t="shared" si="1"/>
+        <v>JeronimoBurgos@gmail.com</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="32" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B109" s="31">
         <v>5559907</v>
       </c>
-      <c r="C109" s="32" t="s">
-        <v>460</v>
+      <c r="C109" t="str">
+        <f t="shared" si="1"/>
+        <v>MarianaDiaz@gmail.com</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -9102,8 +9215,9 @@
       <c r="B110" s="31">
         <v>5559908</v>
       </c>
-      <c r="C110" s="32" t="s">
-        <v>460</v>
+      <c r="C110" t="str">
+        <f t="shared" si="1"/>
+        <v>KarlaMolina@gmail.com</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -9113,8 +9227,9 @@
       <c r="B111" s="31">
         <v>5559909</v>
       </c>
-      <c r="C111" s="32" t="s">
-        <v>460</v>
+      <c r="C111" t="str">
+        <f t="shared" si="1"/>
+        <v>CarlosPosada@gmail.com</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -9124,8 +9239,9 @@
       <c r="B112" s="31">
         <v>5559910</v>
       </c>
-      <c r="C112" s="32" t="s">
-        <v>460</v>
+      <c r="C112" t="str">
+        <f t="shared" si="1"/>
+        <v>AnaJaramillo@gmail.com</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -9135,8 +9251,9 @@
       <c r="B113" s="31">
         <v>5559911</v>
       </c>
-      <c r="C113" s="32" t="s">
-        <v>460</v>
+      <c r="C113" t="str">
+        <f t="shared" si="1"/>
+        <v>VirginiaSaldarriaga@gmail.com</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -9146,19 +9263,21 @@
       <c r="B114" s="31">
         <v>5559912</v>
       </c>
-      <c r="C114" s="32" t="s">
-        <v>460</v>
+      <c r="C114" t="str">
+        <f t="shared" si="1"/>
+        <v>FedericoArroyave@gmail.com</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="32" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B115" s="31">
         <v>5559913</v>
       </c>
-      <c r="C115" s="32" t="s">
-        <v>460</v>
+      <c r="C115" t="str">
+        <f t="shared" si="1"/>
+        <v>LuceroDiaz@gmail.com</v>
       </c>
     </row>
   </sheetData>
